--- a/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week02_07Sep.xlsx
+++ b/Planning/BUILD/Progress_Tees_Valley_BUILD_Weekly_Plan_Week02_07Sep.xlsx
@@ -193,7 +193,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  The floppy-puppet moment does the teaching — no explanation needed before it. Answers built from cards.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA runs the egg-in-a-box demo with the small group. Teacher keeps the three job symbols on display all half-term. LOOP [Feedback Policy]: Voice = match/point/say the job [VF, ?] → Audience: name one job of the skeleton; [R] once received → EVIDENCE: card-match photo, upload same day [E: science — daily EFL; banks ELC 8939].</t>
+    <t xml:space="preserve">TA runs the egg-in-a-box demo with the small group. Teacher keeps the three job symbols on display all half-term. LOOP [Feedback Policy]: Voice = match/point/say the job [VF, ?] → Audience: name one job of the skeleton; [R] once received → EVIDENCE: card-match photo, upload same day [E: science — daily evidence platform; banks ELC 8939].</t>
   </si>
   <si>
     <t xml:space="preserve">Note who gives a JOB rather than a name.  → Influence: 'protect' is the hardest of the three — if it is missing, reteach in W3 with the egg demo again [NS].</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  All sorting is physical; a mark or symbol counts as a signature; pairs chosen by pointing on the first rung.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA referees the relay and scribes reasons beside chosen pairs.  LOOP [Feedback Policy]: Voice = sort/match/choose [VF] → Audience: name the pair back; [R] when the responsibility is shown for real that week → EVIDENCE: charter photo, same day [E: BV/rights — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA referees the relay and scribes reasons beside chosen pairs.  LOOP [Feedback Policy]: Voice = sort/match/choose [VF] → Audience: name the pair back; [R] when the responsibility is shown for real that week → EVIDENCE: charter photo, same day [E: BV/rights — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: the charter becomes live classroom practice → behaviour planning and the BV hub RAG; feeds W3's fair vote [NS].</t>
@@ -247,7 +247,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  Video route replaces reading; pairs matched with picture cards; recording replaces writing throughout.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA supervises handling and scribes what artefacts 'tell us'.  LOOP [Feedback Policy]: Voice = handle/match/say [VF, ?] → Audience: name the pair back; listen to clips fully before tagging, then [R] → EVIDENCE: photo + clip, same day [E: cultural — daily EFL].</t>
+    <t xml:space="preserve">TA supervises handling and scribes what artefacts 'tell us'.  LOOP [Feedback Policy]: Voice = handle/match/say [VF, ?] → Audience: name the pair back; listen to clips fully before tagging, then [R] → EVIDENCE: photo + clip, same day [E: cultural — daily evidence platform].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: who links belief to action vs restates the belief shapes the festivals block starting W3 — record the change made [NS].</t>
@@ -274,7 +274,7 @@
     <t xml:space="preserve">Tiered 3 ways at every step — scaffold, task version and evidence prompt (symbol-supported → sentence-stem → independent): same outcome, different rung. Hands-on route first; easy-read/symbol resources; chunked steps with modelling; movement built into every session.  One finding per station is the ceiling, not the floor; questions asked from picture prompts; findings scribed or recorded.  Pupil A: choice of task &amp; seat, own table, quiet-space option, short 10–20-min goals, opt-out of group sharing. Pupil B: colourblind-safe — labels/patterns/position, never colour alone; movement; offer choice with a reason, not commands. Pupil C: fatigue-aware — soft re-entry after rest, TA checks understanding (he may tick at random), scribe/photo instead of writing. Pupil D: middle seat, fidget/scribble pad, short 10-min bursts, answer or visibly 'park' his questions.</t>
   </si>
   <si>
-    <t xml:space="preserve">TA moves with the group, scribes findings and photographs each station.  LOOP [Feedback Policy]: Voice = point/say a finding, ask a question [VF, ?] → Audience: name the finding back; [R] once received → EVIDENCE: findings sheet photo, same day [E: humanities — daily EFL; banks AQA UAS].</t>
+    <t xml:space="preserve">TA moves with the group, scribes findings and photographs each station.  LOOP [Feedback Policy]: Voice = point/say a finding, ask a question [VF, ?] → Audience: name the finding back; [R] once received → EVIDENCE: findings sheet photo, same day [E: humanities — daily evidence platform; banks AQA UAS].</t>
   </si>
   <si>
     <t xml:space="preserve">Influence: who questions the source vs describes it shapes W3's cause→consequence work — record the change made [NS].</t>
